--- a/src/views/game/zlzq/cardList/dahetaoCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/dahetaoCard/z_level.xlsx
@@ -9,12 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="10560" windowHeight="11880" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="帝国" sheetId="5" r:id="rId1"/>
-    <sheet name="蛮石" sheetId="8" r:id="rId2"/>
-    <sheet name="隐秘" sheetId="7" r:id="rId3"/>
+    <sheet name="蛮石" sheetId="8" r:id="rId1"/>
+    <sheet name="隐秘" sheetId="7" r:id="rId2"/>
+    <sheet name="帝国" sheetId="5" r:id="rId3"/>
     <sheet name="禅意" sheetId="6" r:id="rId4"/>
     <sheet name="大核桃" sheetId="9" r:id="rId5"/>
   </sheets>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="74">
   <si>
     <t>名称</t>
   </si>
@@ -47,6 +47,123 @@
     <t>卡等</t>
   </si>
   <si>
+    <t>旷野猎手</t>
+  </si>
+  <si>
+    <t>势如破竹</t>
+  </si>
+  <si>
+    <t>强行捕猎</t>
+  </si>
+  <si>
+    <t>小计：</t>
+  </si>
+  <si>
+    <t>蓝色卡等：</t>
+  </si>
+  <si>
+    <t>暴怒野人</t>
+  </si>
+  <si>
+    <t>诱敌草人</t>
+  </si>
+  <si>
+    <t>活力仙人掌</t>
+  </si>
+  <si>
+    <t>肥鼠晚宴</t>
+  </si>
+  <si>
+    <t>符文·源力之石</t>
+  </si>
+  <si>
+    <t>飞斧狂人</t>
+  </si>
+  <si>
+    <t>贪食白龙</t>
+  </si>
+  <si>
+    <t>紫色卡等：</t>
+  </si>
+  <si>
+    <t>旷野游侠·大羽</t>
+  </si>
+  <si>
+    <t>比尔&amp;比利</t>
+  </si>
+  <si>
+    <t>血饮烈斧·凯</t>
+  </si>
+  <si>
+    <t>蛮古撼地兽</t>
+  </si>
+  <si>
+    <t>原野大祭师·鲁玛</t>
+  </si>
+  <si>
+    <t>橙色卡等：</t>
+  </si>
+  <si>
+    <t>总计：</t>
+  </si>
+  <si>
+    <t>蛮石卡等：</t>
+  </si>
+  <si>
+    <t>学仆-观测型</t>
+  </si>
+  <si>
+    <t>方尖魔碑</t>
+  </si>
+  <si>
+    <t>沉重否定</t>
+  </si>
+  <si>
+    <t>全数否定</t>
+  </si>
+  <si>
+    <t>隐形术</t>
+  </si>
+  <si>
+    <t>破魔系教授</t>
+  </si>
+  <si>
+    <t>克隆术1</t>
+  </si>
+  <si>
+    <t>克隆术2</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型</t>
+  </si>
+  <si>
+    <t>符文·邪月之夜1</t>
+  </si>
+  <si>
+    <t>符文·邪月之夜2</t>
+  </si>
+  <si>
+    <t>幻域秘树</t>
+  </si>
+  <si>
+    <t>观星台大预言家</t>
+  </si>
+  <si>
+    <t>米拉方舟</t>
+  </si>
+  <si>
+    <t>No.5咒刃·布雷克</t>
+  </si>
+  <si>
+    <t>鬼童-7号</t>
+  </si>
+  <si>
+    <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>隐秘卡等：</t>
+  </si>
+  <si>
     <t>圣殿卫士</t>
   </si>
   <si>
@@ -56,6 +173,9 @@
     <t>炫目神光</t>
   </si>
   <si>
+    <t>塔楼弓手</t>
+  </si>
+  <si>
     <t>田园守望者1</t>
   </si>
   <si>
@@ -65,16 +185,7 @@
     <t>增援战线</t>
   </si>
   <si>
-    <t>光明惩戒1</t>
-  </si>
-  <si>
-    <t>光明惩戒2</t>
-  </si>
-  <si>
-    <t>小计：</t>
-  </si>
-  <si>
-    <t>蓝色卡等：</t>
+    <t>光明惩戒</t>
   </si>
   <si>
     <t>四芒军旗</t>
@@ -86,9 +197,6 @@
     <t>召集护卫</t>
   </si>
   <si>
-    <t>紫色卡等：</t>
-  </si>
-  <si>
     <t>曙光·安娜贝尔</t>
   </si>
   <si>
@@ -101,118 +209,7 @@
     <t>钢铁统帅·雷蒙德</t>
   </si>
   <si>
-    <t>橙色卡等：</t>
-  </si>
-  <si>
-    <t>总计：</t>
-  </si>
-  <si>
     <t>帝国卡等：</t>
-  </si>
-  <si>
-    <t>旷野猎手</t>
-  </si>
-  <si>
-    <t>势如破竹1</t>
-  </si>
-  <si>
-    <t>势如破竹2</t>
-  </si>
-  <si>
-    <t>强行捕猎</t>
-  </si>
-  <si>
-    <t>暴怒野人</t>
-  </si>
-  <si>
-    <t>诱敌草人</t>
-  </si>
-  <si>
-    <t>活力仙人掌</t>
-  </si>
-  <si>
-    <t>肥鼠晚宴</t>
-  </si>
-  <si>
-    <t>符文·源力之石</t>
-  </si>
-  <si>
-    <t>飞斧狂人</t>
-  </si>
-  <si>
-    <t>贪食白龙</t>
-  </si>
-  <si>
-    <t>旷野游侠·大羽</t>
-  </si>
-  <si>
-    <t>比尔&amp;比利</t>
-  </si>
-  <si>
-    <t>血饮烈斧·凯</t>
-  </si>
-  <si>
-    <t>蛮古撼地兽</t>
-  </si>
-  <si>
-    <t>原野大祭师·鲁玛</t>
-  </si>
-  <si>
-    <t>蛮石卡等：</t>
-  </si>
-  <si>
-    <t>学仆-观测型</t>
-  </si>
-  <si>
-    <t>方尖魔碑</t>
-  </si>
-  <si>
-    <t>沉重否定</t>
-  </si>
-  <si>
-    <t>全数否定</t>
-  </si>
-  <si>
-    <t>隐形术</t>
-  </si>
-  <si>
-    <t>破魔系教授</t>
-  </si>
-  <si>
-    <t>克隆术1</t>
-  </si>
-  <si>
-    <t>克隆术2</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型</t>
-  </si>
-  <si>
-    <t>符文·邪月之夜</t>
-  </si>
-  <si>
-    <t>符文·雷火核心</t>
-  </si>
-  <si>
-    <t>幻域秘树</t>
-  </si>
-  <si>
-    <t>观星台大预言家</t>
-  </si>
-  <si>
-    <t>米拉方舟</t>
-  </si>
-  <si>
-    <t>No.5咒刃·布雷克</t>
-  </si>
-  <si>
-    <t>鬼童-7号</t>
-  </si>
-  <si>
-    <t>No.2时光·米拉</t>
-  </si>
-  <si>
-    <t>隐秘卡等：</t>
   </si>
   <si>
     <t>雪庐草人</t>
@@ -1262,7 +1259,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1270,99 +1267,99 @@
         <v>5</v>
       </c>
       <c r="B4" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" s="1">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1">
-        <v>21</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1">
-        <v>21</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1">
+        <f>AVERAGE(C2:C4)</f>
+        <v>23.3333333333333</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B10" s="2">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
         <v>3</v>
       </c>
-      <c r="C7" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="1">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="1">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1">
+      <c r="C12" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>3</v>
+      </c>
+      <c r="C13" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="1">
-        <f>AVERAGE(C2:C9)</f>
-        <v>20.875</v>
-      </c>
-      <c r="D12" s="2"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C15" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1370,22 +1367,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C16" s="2">
         <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2">
-        <v>4</v>
-      </c>
-      <c r="C17" s="2">
-        <v>22</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2"/>
@@ -1393,20 +1384,26 @@
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" s="2" t="s">
+      <c r="A19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="2">
+        <f>AVERAGE(C10:C16)</f>
+        <v>23.1428571428571</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="2">
-        <f>AVERAGE(C15:C17)</f>
-        <v>22.6666666666667</v>
+      <c r="B22" s="3">
+        <v>3</v>
+      </c>
+      <c r="C22" s="3">
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1414,10 +1411,10 @@
         <v>17</v>
       </c>
       <c r="B23" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1425,10 +1422,10 @@
         <v>18</v>
       </c>
       <c r="B24" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" s="3">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1439,7 +1436,7 @@
         <v>6</v>
       </c>
       <c r="C25" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1447,10 +1444,10 @@
         <v>20</v>
       </c>
       <c r="B26" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26" s="3">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1465,14 +1462,14 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C23:C26)</f>
-        <v>20</v>
+        <f>AVERAGE(C22:C26)</f>
+        <v>23.6</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1483,8 +1480,8 @@
         <v>23</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C9,C15:C17,C23:C26)</f>
-        <v>21</v>
+        <f>AVERAGE(C2:C4,C10:C16,C22:C26)</f>
+        <v>23.3333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1494,289 +1491,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="16.375" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="11.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="1">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="1">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="1">
-        <v>2</v>
-      </c>
-      <c r="C4" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="1">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="1">
-        <f>AVERAGE(C2:C5)</f>
-        <v>21.5</v>
-      </c>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="2">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="2">
-        <v>2</v>
-      </c>
-      <c r="C12" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="2">
-        <v>3</v>
-      </c>
-      <c r="C13" s="2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="2">
-        <v>3</v>
-      </c>
-      <c r="C14" s="2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="2">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="2">
-        <v>4</v>
-      </c>
-      <c r="C16" s="2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="2">
-        <v>8</v>
-      </c>
-      <c r="C17" s="2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="2">
-        <f>AVERAGE(C11:C17)</f>
-        <v>23.1428571428571</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="3">
-        <v>3</v>
-      </c>
-      <c r="C23" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="3">
-        <v>4</v>
-      </c>
-      <c r="C24" s="3">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3">
-        <v>5</v>
-      </c>
-      <c r="C25" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3">
-        <v>6</v>
-      </c>
-      <c r="C26" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3">
-        <v>7</v>
-      </c>
-      <c r="C27" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C30" s="3">
-        <f>AVERAGE(C23:C27)</f>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" s="4">
-        <f>AVERAGE(C2:C5,C11:C17,C23:C27)</f>
-        <v>22.6875</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D34"/>
@@ -1800,7 +1514,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -1811,7 +1525,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -1822,7 +1536,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1833,7 +1547,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
@@ -1854,10 +1568,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C8" s="1">
         <f>AVERAGE(C2:C5)</f>
@@ -1867,18 +1581,18 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
@@ -1889,7 +1603,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B13" s="2">
         <v>2</v>
@@ -1900,18 +1614,18 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B14" s="2">
         <v>2</v>
       </c>
       <c r="C14" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B15" s="2">
         <v>3</v>
@@ -1922,7 +1636,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B16" s="2">
         <v>3</v>
@@ -1933,18 +1647,18 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2">
         <v>3</v>
       </c>
       <c r="C17" s="2">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B18" s="2">
         <v>4</v>
@@ -1955,7 +1669,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B19" s="2">
         <v>5</v>
@@ -1966,7 +1680,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="B20" s="2">
         <v>7</v>
@@ -1987,30 +1701,30 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C23" s="2">
         <f>AVERAGE(C11:C20)</f>
-        <v>21.3</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B26" s="3">
         <v>3</v>
       </c>
       <c r="C26" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B27" s="3">
         <v>4</v>
@@ -2021,7 +1735,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B28" s="3">
         <v>5</v>
@@ -2042,14 +1756,14 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C31" s="3">
         <f>AVERAGE(C26:C28)</f>
-        <v>22.6666666666667</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -2057,11 +1771,283 @@
         <v>22</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="C34" s="4">
         <f>AVERAGE(C2:C5,C11:C20,C26:C28)</f>
-        <v>22.0588235294118</v>
+        <v>22.3529411764706</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="1">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="1">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1">
+        <f>AVERAGE(C2:C9)</f>
+        <v>21.5</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="2">
+        <v>2</v>
+      </c>
+      <c r="C16" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="2">
+        <v>4</v>
+      </c>
+      <c r="C17" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="2">
+        <f>AVERAGE(C15:C17)</f>
+        <v>22.6666666666667</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="3">
+        <v>3</v>
+      </c>
+      <c r="C23" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="3">
+        <v>4</v>
+      </c>
+      <c r="C24" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="3">
+        <v>6</v>
+      </c>
+      <c r="C25" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="3">
+        <v>8</v>
+      </c>
+      <c r="C26" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="3">
+        <f>AVERAGE(C23:C26)</f>
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="4">
+        <f>AVERAGE(C2:C9,C15:C17,C23:C26)</f>
+        <v>21.2</v>
       </c>
     </row>
   </sheetData>
@@ -2094,7 +2080,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -2105,7 +2091,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -2116,7 +2102,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -2127,7 +2113,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -2138,7 +2124,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -2149,7 +2135,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -2160,7 +2146,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -2171,7 +2157,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -2182,7 +2168,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B10" s="1">
         <v>4</v>
@@ -2203,10 +2189,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C13" s="1">
         <f>AVERAGE(C2:C10)</f>
@@ -2216,7 +2202,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B16" s="2">
         <v>4</v>
@@ -2227,7 +2213,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B17" s="2">
         <v>4</v>
@@ -2238,7 +2224,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B18" s="2">
         <v>5</v>
@@ -2259,10 +2245,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C21" s="2">
         <f>AVERAGE(C16:C18)</f>
@@ -2271,7 +2257,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B24" s="3">
         <v>3</v>
@@ -2282,7 +2268,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B25" s="3">
         <v>4</v>
@@ -2293,7 +2279,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B26" s="3">
         <v>4</v>
@@ -2314,7 +2300,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>21</v>
@@ -2329,7 +2315,7 @@
         <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C10,C16:C18,C24:C26)</f>

--- a/src/views/game/zlzq/cardList/dahetaoCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/dahetaoCard/z_level.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="10560" windowHeight="11880" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="12480" windowHeight="10200" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="蛮石" sheetId="8" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="73">
   <si>
     <t>名称</t>
   </si>
@@ -113,9 +113,6 @@
     <t>学仆-观测型</t>
   </si>
   <si>
-    <t>方尖魔碑</t>
-  </si>
-  <si>
     <t>沉重否定</t>
   </si>
   <si>
@@ -128,10 +125,7 @@
     <t>破魔系教授</t>
   </si>
   <si>
-    <t>克隆术1</t>
-  </si>
-  <si>
-    <t>克隆术2</t>
+    <t>克隆术</t>
   </si>
   <si>
     <t>学仆-脉冲型</t>
@@ -143,10 +137,13 @@
     <t>符文·邪月之夜2</t>
   </si>
   <si>
+    <t>符文·邪月之夜3</t>
+  </si>
+  <si>
     <t>幻域秘树</t>
   </si>
   <si>
-    <t>观星台大预言家</t>
+    <t>学仆-塑钢型</t>
   </si>
   <si>
     <t>米拉方舟</t>
@@ -170,7 +167,10 @@
     <t>天使琼浆</t>
   </si>
   <si>
-    <t>炫目神光</t>
+    <t>炫目神光1</t>
+  </si>
+  <si>
+    <t>炫目神光2</t>
   </si>
   <si>
     <t>塔楼弓手</t>
@@ -206,18 +206,9 @@
     <t>正阳大主教·伊恩</t>
   </si>
   <si>
-    <t>钢铁统帅·雷蒙德</t>
-  </si>
-  <si>
     <t>帝国卡等：</t>
   </si>
   <si>
-    <t>雪庐草人</t>
-  </si>
-  <si>
-    <t>苦行武僧</t>
-  </si>
-  <si>
     <t>飓风术</t>
   </si>
   <si>
@@ -230,12 +221,15 @@
     <t>连击2</t>
   </si>
   <si>
+    <t>连击3</t>
+  </si>
+  <si>
+    <t>铁山靠</t>
+  </si>
+  <si>
     <t>符文·疾风图腾</t>
   </si>
   <si>
-    <t>铁山靠</t>
-  </si>
-  <si>
     <t>风卷残云</t>
   </si>
   <si>
@@ -243,6 +237,9 @@
   </si>
   <si>
     <t>墨轩隐士</t>
+  </si>
+  <si>
+    <t>萌化术</t>
   </si>
   <si>
     <t>万物之灵</t>
@@ -1493,7 +1490,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="17.75" customWidth="1"/>
@@ -1531,7 +1528,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1539,22 +1536,16 @@
         <v>26</v>
       </c>
       <c r="B4" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="1">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1">
-        <v>24</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1"/>
@@ -1562,29 +1553,35 @@
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="1">
-        <f>AVERAGE(C2:C5)</f>
-        <v>23.5</v>
-      </c>
-      <c r="D8" s="2"/>
+      <c r="C7" s="1">
+        <f>AVERAGE(C2:C4)</f>
+        <v>23.3333333333333</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
+        <v>24</v>
+      </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="2">
         <v>24</v>
@@ -1598,7 +1595,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1606,10 +1603,10 @@
         <v>30</v>
       </c>
       <c r="B13" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" s="2">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1617,10 +1614,10 @@
         <v>31</v>
       </c>
       <c r="B14" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1631,7 +1628,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1642,7 +1639,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1650,7 +1647,7 @@
         <v>34</v>
       </c>
       <c r="B17" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" s="2">
         <v>24</v>
@@ -1672,22 +1669,16 @@
         <v>36</v>
       </c>
       <c r="B19" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C19" s="2">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="2">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2">
-        <v>24</v>
-      </c>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2"/>
@@ -1695,20 +1686,26 @@
       <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
+      <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="2">
-        <f>AVERAGE(C11:C20)</f>
-        <v>21.7</v>
+      <c r="C22" s="2">
+        <f>AVERAGE(C10:C19)</f>
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3">
+        <v>3</v>
+      </c>
+      <c r="C25" s="3">
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1716,7 +1713,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" s="3">
         <v>24</v>
@@ -1727,22 +1724,16 @@
         <v>39</v>
       </c>
       <c r="B27" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="3">
-        <v>5</v>
-      </c>
-      <c r="C28" s="3">
-        <v>21</v>
-      </c>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3"/>
@@ -1750,32 +1741,27 @@
       <c r="C29" s="3"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="3" t="s">
+      <c r="A30" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B30" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C31" s="3">
-        <f>AVERAGE(C26:C28)</f>
+      <c r="C30" s="3">
+        <f>AVERAGE(C25:C27)</f>
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="4" t="s">
+    <row r="33" spans="1:3">
+      <c r="A33" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C34" s="4">
-        <f>AVERAGE(C2:C5,C11:C20,C26:C28)</f>
-        <v>22.3529411764706</v>
+      <c r="B33" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" s="4">
+        <f>AVERAGE(C2:C4,C10:C19,C25:C27)</f>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1808,7 +1794,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -1819,7 +1805,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -1830,7 +1816,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1841,63 +1827,69 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
       </c>
       <c r="C8" s="1">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="1">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B10" s="1">
         <v>5</v>
       </c>
-      <c r="C9" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
+      <c r="C10" s="1">
+        <v>23</v>
+      </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1"/>
@@ -1905,55 +1897,55 @@
       <c r="C11" s="1"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="1">
-        <f>AVERAGE(C2:C9)</f>
-        <v>21.5</v>
-      </c>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="2">
-        <v>1</v>
-      </c>
-      <c r="C15" s="2">
-        <v>22</v>
-      </c>
+      <c r="C13" s="1">
+        <f>AVERAGE(C2:C10)</f>
+        <v>21.6666666666667</v>
+      </c>
+      <c r="D13" s="2"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="2">
+        <v>2</v>
+      </c>
+      <c r="C17" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B18" s="2">
         <v>4</v>
       </c>
-      <c r="C17" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="C18" s="2">
+        <v>23</v>
+      </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2"/>
@@ -1961,59 +1953,53 @@
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="2">
-        <f>AVERAGE(C15:C17)</f>
-        <v>22.6666666666667</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B23" s="3">
-        <v>3</v>
-      </c>
-      <c r="C23" s="3">
-        <v>22</v>
+      <c r="C21" s="2">
+        <f>AVERAGE(C16:C18)</f>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B24" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24" s="3">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B25" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C25" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B26" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C26" s="3">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2034,8 +2020,8 @@
         <v>21</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C23:C26)</f>
-        <v>19.5</v>
+        <f>AVERAGE(C24:C26)</f>
+        <v>21.6666666666667</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2043,11 +2029,11 @@
         <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C9,C15:C17,C23:C26)</f>
-        <v>21.2</v>
+        <f>AVERAGE(C2:C10,C16:C18,C24:C26)</f>
+        <v>21.9333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2080,10 +2066,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B2" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1">
         <v>19</v>
@@ -2091,21 +2077,21 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B4" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1">
         <v>19</v>
@@ -2113,18 +2099,18 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -2135,7 +2121,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -2146,36 +2132,30 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
       </c>
       <c r="C8" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B9" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" s="1">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" s="1">
-        <v>4</v>
-      </c>
-      <c r="C10" s="1">
-        <v>19</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1"/>
@@ -2183,48 +2163,54 @@
       <c r="C11" s="1"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
+      <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="1">
-        <f>AVERAGE(C2:C10)</f>
-        <v>18.1111111111111</v>
-      </c>
-      <c r="D13" s="2"/>
+      <c r="C12" s="1">
+        <f>AVERAGE(C2:C9)</f>
+        <v>18.375</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="2">
+        <v>4</v>
+      </c>
+      <c r="C15" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B16" s="2">
         <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17" s="2">
         <v>4</v>
       </c>
       <c r="C17" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B18" s="2">
         <v>5</v>
@@ -2251,24 +2237,24 @@
         <v>15</v>
       </c>
       <c r="C21" s="2">
-        <f>AVERAGE(C16:C18)</f>
-        <v>20</v>
+        <f>AVERAGE(C15:C18)</f>
+        <v>18.25</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B24" s="3">
         <v>3</v>
       </c>
       <c r="C24" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B25" s="3">
         <v>4</v>
@@ -2279,13 +2265,13 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B26" s="3">
         <v>4</v>
       </c>
       <c r="C26" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2307,7 +2293,7 @@
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C24:C26)</f>
-        <v>16.3333333333333</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2315,11 +2301,11 @@
         <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C10,C16:C18,C24:C26)</f>
-        <v>18.1333333333333</v>
+        <f>AVERAGE(C2:C9,C15:C18,C24:C26)</f>
+        <v>18.0666666666667</v>
       </c>
     </row>
   </sheetData>
